--- a/SRE_Preset.xlsx
+++ b/SRE_Preset.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://appriver3651001394-my.sharepoint.com/personal/alaina_defranco_us_q-cells_com/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="120" documentId="8_{A9410A73-9117-4A39-950D-6C9CF83691C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C13AF44C-CFD8-4245-B5B3-662211C98164}"/>
+  <xr:revisionPtr revIDLastSave="124" documentId="8_{A9410A73-9117-4A39-950D-6C9CF83691C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5886A484-A38F-46E2-98DD-1AE3319DF471}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C553B2AE-5A13-4E4D-A89F-62275D00D177}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{C553B2AE-5A13-4E4D-A89F-62275D00D177}"/>
   </bookViews>
   <sheets>
     <sheet name="Select" sheetId="3" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -269,14 +269,14 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -294,10 +294,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -632,35 +628,35 @@
       <c r="A3" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="8"/>
-      <c r="J3" s="8"/>
-      <c r="K3" s="8"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="9"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="9"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="9"/>
-      <c r="K4" s="9"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="10"/>
+      <c r="J4" s="10"/>
+      <c r="K4" s="10"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
@@ -809,7 +805,7 @@
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="10" t="s">
+      <c r="A12" s="8" t="s">
         <v>13</v>
       </c>
       <c r="B12" t="str">
@@ -868,18 +864,18 @@
       <c r="A3" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="8"/>
-      <c r="J3" s="8"/>
-      <c r="K3" s="8"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="9"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="9"/>
       <c r="P3" t="s">
         <v>16</v>
       </c>
@@ -891,18 +887,18 @@
       <c r="A4" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="9"/>
-      <c r="K4" s="9"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="10"/>
+      <c r="J4" s="10"/>
+      <c r="K4" s="10"/>
       <c r="P4" t="s">
         <v>20</v>
       </c>
@@ -1050,7 +1046,7 @@
         <v>4</v>
       </c>
       <c r="B9" s="5">
-        <v>42</v>
+        <v>67</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
@@ -1058,7 +1054,7 @@
         <v>5</v>
       </c>
       <c r="B10" s="5">
-        <v>42</v>
+        <v>67</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
@@ -1070,7 +1066,7 @@
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A12" s="10" t="s">
+      <c r="A12" s="8" t="s">
         <v>13</v>
       </c>
       <c r="B12" t="s">
@@ -1081,35 +1077,35 @@
       <c r="A14" t="s">
         <v>11</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="8"/>
-      <c r="H14" s="8"/>
-      <c r="I14" s="8"/>
-      <c r="J14" s="8"/>
-      <c r="K14" s="8"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="9"/>
+      <c r="G14" s="9"/>
+      <c r="H14" s="9"/>
+      <c r="I14" s="9"/>
+      <c r="J14" s="9"/>
+      <c r="K14" s="9"/>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="9" t="s">
+      <c r="B15" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="9"/>
-      <c r="J15" s="9"/>
-      <c r="K15" s="9"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="10"/>
+      <c r="H15" s="10"/>
+      <c r="I15" s="10"/>
+      <c r="J15" s="10"/>
+      <c r="K15" s="10"/>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
@@ -1244,7 +1240,7 @@
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" s="10" t="s">
+      <c r="A23" s="8" t="s">
         <v>13</v>
       </c>
       <c r="B23" t="s">
@@ -1255,35 +1251,35 @@
       <c r="A25" t="s">
         <v>11</v>
       </c>
-      <c r="B25" s="8" t="s">
+      <c r="B25" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C25" s="8"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="8"/>
-      <c r="G25" s="8"/>
-      <c r="H25" s="8"/>
-      <c r="I25" s="8"/>
-      <c r="J25" s="8"/>
-      <c r="K25" s="8"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="9"/>
+      <c r="F25" s="9"/>
+      <c r="G25" s="9"/>
+      <c r="H25" s="9"/>
+      <c r="I25" s="9"/>
+      <c r="J25" s="9"/>
+      <c r="K25" s="9"/>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>9</v>
       </c>
-      <c r="B26" s="9" t="s">
+      <c r="B26" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C26" s="9"/>
-      <c r="D26" s="9"/>
-      <c r="E26" s="9"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="9"/>
-      <c r="H26" s="9"/>
-      <c r="I26" s="9"/>
-      <c r="J26" s="9"/>
-      <c r="K26" s="9"/>
+      <c r="C26" s="10"/>
+      <c r="D26" s="10"/>
+      <c r="E26" s="10"/>
+      <c r="F26" s="10"/>
+      <c r="G26" s="10"/>
+      <c r="H26" s="10"/>
+      <c r="I26" s="10"/>
+      <c r="J26" s="10"/>
+      <c r="K26" s="10"/>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
@@ -1426,7 +1422,7 @@
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A34" s="10" t="s">
+      <c r="A34" s="8" t="s">
         <v>13</v>
       </c>
       <c r="B34" t="s">
@@ -1437,35 +1433,35 @@
       <c r="A36" t="s">
         <v>11</v>
       </c>
-      <c r="B36" s="8" t="s">
+      <c r="B36" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C36" s="8"/>
-      <c r="D36" s="8"/>
-      <c r="E36" s="8"/>
-      <c r="F36" s="8"/>
-      <c r="G36" s="8"/>
-      <c r="H36" s="8"/>
-      <c r="I36" s="8"/>
-      <c r="J36" s="8"/>
-      <c r="K36" s="8"/>
+      <c r="C36" s="9"/>
+      <c r="D36" s="9"/>
+      <c r="E36" s="9"/>
+      <c r="F36" s="9"/>
+      <c r="G36" s="9"/>
+      <c r="H36" s="9"/>
+      <c r="I36" s="9"/>
+      <c r="J36" s="9"/>
+      <c r="K36" s="9"/>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>9</v>
       </c>
-      <c r="B37" s="9" t="s">
+      <c r="B37" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C37" s="9"/>
-      <c r="D37" s="9"/>
-      <c r="E37" s="9"/>
-      <c r="F37" s="9"/>
-      <c r="G37" s="9"/>
-      <c r="H37" s="9"/>
-      <c r="I37" s="9"/>
-      <c r="J37" s="9"/>
-      <c r="K37" s="9"/>
+      <c r="C37" s="10"/>
+      <c r="D37" s="10"/>
+      <c r="E37" s="10"/>
+      <c r="F37" s="10"/>
+      <c r="G37" s="10"/>
+      <c r="H37" s="10"/>
+      <c r="I37" s="10"/>
+      <c r="J37" s="10"/>
+      <c r="K37" s="10"/>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
@@ -1608,7 +1604,7 @@
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A45" s="10" t="s">
+      <c r="A45" s="8" t="s">
         <v>13</v>
       </c>
       <c r="B45" t="s">
@@ -1619,35 +1615,35 @@
       <c r="A47" t="s">
         <v>11</v>
       </c>
-      <c r="B47" s="8" t="s">
+      <c r="B47" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C47" s="8"/>
-      <c r="D47" s="8"/>
-      <c r="E47" s="8"/>
-      <c r="F47" s="8"/>
-      <c r="G47" s="8"/>
-      <c r="H47" s="8"/>
-      <c r="I47" s="8"/>
-      <c r="J47" s="8"/>
-      <c r="K47" s="8"/>
+      <c r="C47" s="9"/>
+      <c r="D47" s="9"/>
+      <c r="E47" s="9"/>
+      <c r="F47" s="9"/>
+      <c r="G47" s="9"/>
+      <c r="H47" s="9"/>
+      <c r="I47" s="9"/>
+      <c r="J47" s="9"/>
+      <c r="K47" s="9"/>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>9</v>
       </c>
-      <c r="B48" s="9" t="s">
+      <c r="B48" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C48" s="9"/>
-      <c r="D48" s="9"/>
-      <c r="E48" s="9"/>
-      <c r="F48" s="9"/>
-      <c r="G48" s="9"/>
-      <c r="H48" s="9"/>
-      <c r="I48" s="9"/>
-      <c r="J48" s="9"/>
-      <c r="K48" s="9"/>
+      <c r="C48" s="10"/>
+      <c r="D48" s="10"/>
+      <c r="E48" s="10"/>
+      <c r="F48" s="10"/>
+      <c r="G48" s="10"/>
+      <c r="H48" s="10"/>
+      <c r="I48" s="10"/>
+      <c r="J48" s="10"/>
+      <c r="K48" s="10"/>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
@@ -1790,7 +1786,7 @@
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A56" s="10" t="s">
+      <c r="A56" s="8" t="s">
         <v>13</v>
       </c>
       <c r="B56" t="s">
@@ -1799,16 +1795,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="B3:K3"/>
+    <mergeCell ref="B4:K4"/>
+    <mergeCell ref="B14:K14"/>
+    <mergeCell ref="B15:K15"/>
     <mergeCell ref="B48:K48"/>
     <mergeCell ref="B25:K25"/>
     <mergeCell ref="B26:K26"/>
     <mergeCell ref="B36:K36"/>
     <mergeCell ref="B37:K37"/>
     <mergeCell ref="B47:K47"/>
-    <mergeCell ref="B3:K3"/>
-    <mergeCell ref="B4:K4"/>
-    <mergeCell ref="B14:K14"/>
-    <mergeCell ref="B15:K15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SRE_Preset.xlsx
+++ b/SRE_Preset.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://appriver3651001394-my.sharepoint.com/personal/alaina_defranco_us_q-cells_com/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="124" documentId="8_{A9410A73-9117-4A39-950D-6C9CF83691C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5886A484-A38F-46E2-98DD-1AE3319DF471}"/>
+  <xr:revisionPtr revIDLastSave="120" documentId="8_{A9410A73-9117-4A39-950D-6C9CF83691C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C13AF44C-CFD8-4245-B5B3-662211C98164}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{C553B2AE-5A13-4E4D-A89F-62275D00D177}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C553B2AE-5A13-4E4D-A89F-62275D00D177}"/>
   </bookViews>
   <sheets>
     <sheet name="Select" sheetId="3" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -269,14 +269,14 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -294,6 +294,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -628,35 +632,35 @@
       <c r="A3" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="9"/>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="9"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="9"/>
-      <c r="J3" s="9"/>
-      <c r="K3" s="9"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="8"/>
+      <c r="J3" s="8"/>
+      <c r="K3" s="8"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="10"/>
-      <c r="K4" s="10"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
@@ -805,7 +809,7 @@
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="10" t="s">
         <v>13</v>
       </c>
       <c r="B12" t="str">
@@ -864,18 +868,18 @@
       <c r="A3" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="9"/>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="9"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="9"/>
-      <c r="J3" s="9"/>
-      <c r="K3" s="9"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="8"/>
+      <c r="J3" s="8"/>
+      <c r="K3" s="8"/>
       <c r="P3" t="s">
         <v>16</v>
       </c>
@@ -887,18 +891,18 @@
       <c r="A4" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="10"/>
-      <c r="K4" s="10"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
       <c r="P4" t="s">
         <v>20</v>
       </c>
@@ -1046,7 +1050,7 @@
         <v>4</v>
       </c>
       <c r="B9" s="5">
-        <v>67</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
@@ -1054,7 +1058,7 @@
         <v>5</v>
       </c>
       <c r="B10" s="5">
-        <v>67</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
@@ -1066,7 +1070,7 @@
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="10" t="s">
         <v>13</v>
       </c>
       <c r="B12" t="s">
@@ -1077,35 +1081,35 @@
       <c r="A14" t="s">
         <v>11</v>
       </c>
-      <c r="B14" s="9" t="s">
+      <c r="B14" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="9"/>
-      <c r="J14" s="9"/>
-      <c r="K14" s="9"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="8"/>
+      <c r="K14" s="8"/>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="10" t="s">
+      <c r="B15" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C15" s="10"/>
-      <c r="D15" s="10"/>
-      <c r="E15" s="10"/>
-      <c r="F15" s="10"/>
-      <c r="G15" s="10"/>
-      <c r="H15" s="10"/>
-      <c r="I15" s="10"/>
-      <c r="J15" s="10"/>
-      <c r="K15" s="10"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="9"/>
+      <c r="G15" s="9"/>
+      <c r="H15" s="9"/>
+      <c r="I15" s="9"/>
+      <c r="J15" s="9"/>
+      <c r="K15" s="9"/>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
@@ -1240,7 +1244,7 @@
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" s="8" t="s">
+      <c r="A23" s="10" t="s">
         <v>13</v>
       </c>
       <c r="B23" t="s">
@@ -1251,35 +1255,35 @@
       <c r="A25" t="s">
         <v>11</v>
       </c>
-      <c r="B25" s="9" t="s">
+      <c r="B25" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9"/>
-      <c r="E25" s="9"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="9"/>
-      <c r="H25" s="9"/>
-      <c r="I25" s="9"/>
-      <c r="J25" s="9"/>
-      <c r="K25" s="9"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="8"/>
+      <c r="G25" s="8"/>
+      <c r="H25" s="8"/>
+      <c r="I25" s="8"/>
+      <c r="J25" s="8"/>
+      <c r="K25" s="8"/>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>9</v>
       </c>
-      <c r="B26" s="10" t="s">
+      <c r="B26" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C26" s="10"/>
-      <c r="D26" s="10"/>
-      <c r="E26" s="10"/>
-      <c r="F26" s="10"/>
-      <c r="G26" s="10"/>
-      <c r="H26" s="10"/>
-      <c r="I26" s="10"/>
-      <c r="J26" s="10"/>
-      <c r="K26" s="10"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="9"/>
+      <c r="F26" s="9"/>
+      <c r="G26" s="9"/>
+      <c r="H26" s="9"/>
+      <c r="I26" s="9"/>
+      <c r="J26" s="9"/>
+      <c r="K26" s="9"/>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
@@ -1422,7 +1426,7 @@
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A34" s="8" t="s">
+      <c r="A34" s="10" t="s">
         <v>13</v>
       </c>
       <c r="B34" t="s">
@@ -1433,35 +1437,35 @@
       <c r="A36" t="s">
         <v>11</v>
       </c>
-      <c r="B36" s="9" t="s">
+      <c r="B36" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C36" s="9"/>
-      <c r="D36" s="9"/>
-      <c r="E36" s="9"/>
-      <c r="F36" s="9"/>
-      <c r="G36" s="9"/>
-      <c r="H36" s="9"/>
-      <c r="I36" s="9"/>
-      <c r="J36" s="9"/>
-      <c r="K36" s="9"/>
+      <c r="C36" s="8"/>
+      <c r="D36" s="8"/>
+      <c r="E36" s="8"/>
+      <c r="F36" s="8"/>
+      <c r="G36" s="8"/>
+      <c r="H36" s="8"/>
+      <c r="I36" s="8"/>
+      <c r="J36" s="8"/>
+      <c r="K36" s="8"/>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>9</v>
       </c>
-      <c r="B37" s="10" t="s">
+      <c r="B37" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C37" s="10"/>
-      <c r="D37" s="10"/>
-      <c r="E37" s="10"/>
-      <c r="F37" s="10"/>
-      <c r="G37" s="10"/>
-      <c r="H37" s="10"/>
-      <c r="I37" s="10"/>
-      <c r="J37" s="10"/>
-      <c r="K37" s="10"/>
+      <c r="C37" s="9"/>
+      <c r="D37" s="9"/>
+      <c r="E37" s="9"/>
+      <c r="F37" s="9"/>
+      <c r="G37" s="9"/>
+      <c r="H37" s="9"/>
+      <c r="I37" s="9"/>
+      <c r="J37" s="9"/>
+      <c r="K37" s="9"/>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
@@ -1604,7 +1608,7 @@
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A45" s="8" t="s">
+      <c r="A45" s="10" t="s">
         <v>13</v>
       </c>
       <c r="B45" t="s">
@@ -1615,35 +1619,35 @@
       <c r="A47" t="s">
         <v>11</v>
       </c>
-      <c r="B47" s="9" t="s">
+      <c r="B47" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C47" s="9"/>
-      <c r="D47" s="9"/>
-      <c r="E47" s="9"/>
-      <c r="F47" s="9"/>
-      <c r="G47" s="9"/>
-      <c r="H47" s="9"/>
-      <c r="I47" s="9"/>
-      <c r="J47" s="9"/>
-      <c r="K47" s="9"/>
+      <c r="C47" s="8"/>
+      <c r="D47" s="8"/>
+      <c r="E47" s="8"/>
+      <c r="F47" s="8"/>
+      <c r="G47" s="8"/>
+      <c r="H47" s="8"/>
+      <c r="I47" s="8"/>
+      <c r="J47" s="8"/>
+      <c r="K47" s="8"/>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>9</v>
       </c>
-      <c r="B48" s="10" t="s">
+      <c r="B48" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C48" s="10"/>
-      <c r="D48" s="10"/>
-      <c r="E48" s="10"/>
-      <c r="F48" s="10"/>
-      <c r="G48" s="10"/>
-      <c r="H48" s="10"/>
-      <c r="I48" s="10"/>
-      <c r="J48" s="10"/>
-      <c r="K48" s="10"/>
+      <c r="C48" s="9"/>
+      <c r="D48" s="9"/>
+      <c r="E48" s="9"/>
+      <c r="F48" s="9"/>
+      <c r="G48" s="9"/>
+      <c r="H48" s="9"/>
+      <c r="I48" s="9"/>
+      <c r="J48" s="9"/>
+      <c r="K48" s="9"/>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
@@ -1786,7 +1790,7 @@
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A56" s="8" t="s">
+      <c r="A56" s="10" t="s">
         <v>13</v>
       </c>
       <c r="B56" t="s">
@@ -1795,16 +1799,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="B3:K3"/>
-    <mergeCell ref="B4:K4"/>
-    <mergeCell ref="B14:K14"/>
-    <mergeCell ref="B15:K15"/>
     <mergeCell ref="B48:K48"/>
     <mergeCell ref="B25:K25"/>
     <mergeCell ref="B26:K26"/>
     <mergeCell ref="B36:K36"/>
     <mergeCell ref="B37:K37"/>
     <mergeCell ref="B47:K47"/>
+    <mergeCell ref="B3:K3"/>
+    <mergeCell ref="B4:K4"/>
+    <mergeCell ref="B14:K14"/>
+    <mergeCell ref="B15:K15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
